--- a/04_DESIGN_TABLES/DesignTable_5404N.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5404N.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1310,14 +1310,37 @@
           <t>5404-N-04X2.500</t>
         </is>
       </c>
+      <c r="B17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>5404-N-04X2.500</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 2.5 in</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1327,7 +1350,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1347,14 +1370,37 @@
           <t>5404-N-04X3.500</t>
         </is>
       </c>
+      <c r="B18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>5404-N-04X3.500</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 3.5 in</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1364,7 +1410,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1384,14 +1430,37 @@
           <t>5404-N-04X4.000</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>5404-N-04X4.000</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 4 in</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1401,7 +1470,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1421,14 +1490,37 @@
           <t>5404-N-04X4.500</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>5404-N-04X4.500</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 4.5 in</t>
+        </is>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1438,7 +1530,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1458,14 +1550,37 @@
           <t>5404-N-04X5.000</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>5404-N-04X5.000</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 5 in</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1475,7 +1590,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1495,14 +1610,37 @@
           <t>5404-N-04X5.500</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>5404-N-04X5.500</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 5.5 in</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1512,7 +1650,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1532,14 +1670,37 @@
           <t>5404-N-04X6.000</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.54</v>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>5404-N-04X6.000</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1/4-18 x 1/4-18 NPTF, cut length 6 in</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1549,7 +1710,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-04-04-X2 (A4 yes 2026-10-18); Brennan prints a different through drill 0.281 (A1 / A2 DRILL) vs the Air-Way transfer 0.3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1569,14 +1730,37 @@
           <t>5404-N-06X2.000</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>5404-N-06X2.000</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 2 in</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1586,7 +1770,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1606,14 +1790,37 @@
           <t>5404-N-06X2.500</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>5404-N-06X2.500</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 2.5 in</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1623,7 +1830,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1643,14 +1850,37 @@
           <t>5404-N-06X3.000</t>
         </is>
       </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>5404-N-06X3.000</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 3 in</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1660,7 +1890,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -1680,14 +1910,37 @@
           <t>5404-N-06X3.500</t>
         </is>
       </c>
+      <c r="B27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>5404-N-06X3.500</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 3.5 in</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1697,7 +1950,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan catalog row misprinted: A1 / A2 DRILL = 3.500 / 88.90 (the length in inch and mm; verify/png/TFA_p12_L3.png)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -1717,14 +1970,37 @@
           <t>5404-N-06X4.000</t>
         </is>
       </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>5404-N-06X4.000</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 4 in</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1734,7 +2010,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -1791,14 +2067,37 @@
           <t>5404-N-06X5.000</t>
         </is>
       </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>5404-N-06X5.000</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 5 in</t>
+        </is>
+      </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1808,7 +2107,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -1828,14 +2127,37 @@
           <t>5404-N-06X6.000</t>
         </is>
       </c>
+      <c r="B31" t="n">
+        <v>6</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>5404-N-06X6.000</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 6 in</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1845,7 +2167,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); Brennan prints a different through drill 0.406 (A1 / A2 DRILL) vs the Air-Way transfer 0.39</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -1902,14 +2224,37 @@
           <t>5404-N-08X3.500</t>
         </is>
       </c>
+      <c r="B33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>5404-N-08X3.500</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/2-14 NPTF, cut length 3.5 in</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -1919,7 +2264,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -1939,14 +2284,37 @@
           <t>5404-N-08X4.500</t>
         </is>
       </c>
+      <c r="B34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>5404-N-08X4.500</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/2-14 NPTF, cut length 4.5 in</t>
+        </is>
+      </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1956,7 +2324,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -1976,14 +2344,37 @@
           <t>5404-N-08X5.000</t>
         </is>
       </c>
+      <c r="B35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
           <t>5404-N-08X5.000</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/2-14 NPTF, cut length 5 in</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -1993,7 +2384,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2050,34 +2441,117 @@
           <t>5404-N-08X6.000</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>6</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>5404-N-08X6.000</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/2-14 NPTF, cut length 6 in</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L from the part number (= Brennan catalog), bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18); Brennan prints a different through drill 0.531 (A1 / A2 DRILL) vs the Air-Way transfer 0.48</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>BUILD</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>5404-N-08X6.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.500</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.500</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 5.5 in</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>MISSING</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; L from the part number (= Brennan TFA p.11); bar dia / bores from the Air-Way nipple 5404-N-06-06-X1 (A4 transfer); NPTF ends ASME</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); no Brennan size used</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
         <is>
           <t>BUILD</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>5404-N-08X6.000</t>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>5404-N-06X5.500</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_5404N.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5404N.xlsx
@@ -2030,14 +2030,37 @@
           <t>5404-N-06X4.500</t>
         </is>
       </c>
+      <c r="B29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.675</v>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>5404-N-06X4.500</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>3/8-18 x 3/8-18 NPTF, cut length 4.5 in</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2047,7 +2070,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18), as every 06 sibling row; MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2187,14 +2210,37 @@
           <t>5404-N-08X2.500</t>
         </is>
       </c>
+      <c r="B32" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>5404-N-08X2.500</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/2-14 NPTF, cut length 2.5 in</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2204,7 +2250,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18), as every 08 sibling row; MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2404,14 +2450,37 @@
           <t>5404-N-08X5.500</t>
         </is>
       </c>
+      <c r="B36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H36" t="inlineStr">
         <is>
           <t>5404-N-08X5.500</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1/2-14 x 1/2-14 NPTF, cut length 5.5 in</t>
+        </is>
+      </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2421,7 +2490,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-08-08-X3 (A4 yes 2026-10-18), as every 08 sibling row; MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2531,7 +2600,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2541,7 +2610,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); no Brennan size used</t>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18); no Brennan size used | 2026-10-21 (batch 20): L from the part number, bar dia and bores from the Air-Way nipple 5404-N-06-06-X1 (A4 yes 2026-10-18), as every 06 sibling row; MISSING -&gt; ASSUMED</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
